--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104669_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104669_W24.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3656</v>
+        <v>3.4236</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6543</v>
+        <v>3.786</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7113</v>
+        <v>-0.3624</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4955</v>
+        <v>4.5847</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9437</v>
+        <v>-1.5029</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5517</v>
+        <v>6.0876</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9794</v>
+        <v>6.13</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7636</v>
+        <v>-0.669</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2158</v>
+        <v>6.799</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4839</v>
+        <v>-1.5453</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8198</v>
+        <v>-0.8339</v>
       </c>
       <c r="O2" t="n">
-        <v>0.336</v>
+        <v>-0.7114</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5091</v>
+        <v>0.1835</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3288</v>
+        <v>-0.019</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1802</v>
+        <v>0.2025</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.639</v>
+        <v>0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.13</v>
+        <v>2.6882</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5915</v>
+        <v>4.0329</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4616</v>
+        <v>-1.3447</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5819</v>
+        <v>1.7197</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5168</v>
+        <v>1.2522</v>
       </c>
       <c r="I3" t="n">
-        <v>6.0986</v>
+        <v>0.4674</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1584</v>
+        <v>2.4628</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6651</v>
+        <v>1.1376</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8236</v>
+        <v>1.3252</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5765</v>
+        <v>-0.7432</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8516</v>
+        <v>0.1146</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7249</v>
+        <v>-0.8578</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1155</v>
+        <v>0.058</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2571</v>
+        <v>0.4806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1415</v>
+        <v>-0.4226</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7814</v>
+        <v>2.5369</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2586</v>
+        <v>3.8394</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4773</v>
+        <v>-1.3024</v>
       </c>
       <c r="G4" t="n">
-        <v>8.039099999999999</v>
+        <v>0.6066</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3621</v>
+        <v>-0.1356</v>
       </c>
       <c r="I4" t="n">
-        <v>6.677</v>
+        <v>0.7421</v>
       </c>
       <c r="J4" t="n">
-        <v>8.405099999999999</v>
+        <v>2.4228</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2614</v>
+        <v>0.3825</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1437</v>
+        <v>2.0404</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3661</v>
+        <v>-1.8163</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8993</v>
+        <v>-0.518</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5333</v>
+        <v>-1.2982</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.9488</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4228</v>
+        <v>0.0199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3902</v>
+        <v>0.3271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0326</v>
+        <v>-0.3072</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7317</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7317</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6844</v>
+        <v>2.3953</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1694</v>
+        <v>4.073</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.485</v>
+        <v>-1.6777</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7269</v>
+        <v>8.0246</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2525</v>
+        <v>1.3668</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4744</v>
+        <v>6.6577</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4809</v>
+        <v>8.3498</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1429</v>
+        <v>2.244</v>
       </c>
       <c r="L5" t="n">
-        <v>1.338</v>
+        <v>6.1057</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.754</v>
+        <v>-0.3252</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1096</v>
+        <v>-0.8772</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8636</v>
+        <v>0.552</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0502</v>
+        <v>0.0536</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5958</v>
+        <v>0.2759</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5456</v>
+        <v>-0.2223</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5018</v>
+        <v>1.3016</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5597</v>
+        <v>-0.0265</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0579</v>
+        <v>1.3281</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5898</v>
+        <v>0.5331</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1459</v>
+        <v>-0.1808</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7357</v>
+        <v>0.7139</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4409</v>
+        <v>0.9196</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3912</v>
+        <v>0.8823</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0497</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8511</v>
+        <v>-0.3865</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5371</v>
+        <v>-1.0631</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.314</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9954</v>
+        <v>-0.547</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9739</v>
+        <v>-0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0215</v>
+        <v>-0.2658</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.8603</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.4733</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8986</v>
+        <v>1.2818</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1901</v>
+        <v>1.0332</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0887</v>
+        <v>0.2486</v>
       </c>
       <c r="G7" t="n">
-        <v>0.529</v>
+        <v>2.4885</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1774</v>
+        <v>1.9389</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7064</v>
+        <v>0.5496</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9307</v>
+        <v>2.9443</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8934</v>
+        <v>2.7439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.2004</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4017</v>
+        <v>-0.4558</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0708</v>
+        <v>-0.805</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6691</v>
+        <v>0.3492</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9518</v>
+        <v>0.4275</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4688</v>
+        <v>0.7521</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.483</v>
+        <v>-0.3246</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8678</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4822</v>
+        <v>-0.387</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,55 +1033,55 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5899</v>
+        <v>-0.5184</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9777</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3878</v>
+        <v>0.3934</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2885</v>
+        <v>-1.2895</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5022</v>
+        <v>-0.4999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2087</v>
+        <v>-0.1394</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>-0.1394</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4059</v>
+        <v>-0.8032</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4305</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9754</v>
+        <v>-0.9033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1402</v>
+        <v>0.1421</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1313</v>
+        <v>-1.1316</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2715</v>
+        <v>1.2737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9819</v>
+        <v>0.9735</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2495</v>
+        <v>-0.2553</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8656</v>
+        <v>-0.2625</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>0.2647</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5873</v>
+        <v>-0.5272</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3921</v>
+        <v>-3.2112</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9129</v>
+        <v>-3.1729</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4792</v>
+        <v>-0.0384</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9166</v>
+        <v>-2.9161</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9943</v>
+        <v>-1.9878</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9223</v>
+        <v>-0.9283</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8645</v>
+        <v>-2.8892</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1744</v>
+        <v>-1.1828</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6901</v>
+        <v>-1.7063</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0521</v>
+        <v>-0.027</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.878</v>
+        <v>-0.7096</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8296</v>
+        <v>-0.4259</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7802</v>
+        <v>-3.6498</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8893</v>
+        <v>-2.8453</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8909</v>
+        <v>-0.8045</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7074</v>
+        <v>-3.7058</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9726</v>
+        <v>-0.9709</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7348</v>
+        <v>-2.7349</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1703</v>
+        <v>-2.1878</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5371</v>
+        <v>-1.518</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0974</v>
+        <v>0.0349</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4567</v>
+        <v>0.5294</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5541</v>
+        <v>-0.4945</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8573</v>
+        <v>-4.7517</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.676</v>
+        <v>-1.7008</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1813</v>
+        <v>-3.0509</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2693</v>
+        <v>-4.26</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8197</v>
+        <v>-1.8127</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4496</v>
+        <v>-2.4473</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3891</v>
+        <v>-1.412</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.232</v>
+        <v>-0.2464</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8801</v>
+        <v>-2.848</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3439</v>
+        <v>0.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6866</v>
+        <v>0.6917</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3427</v>
+        <v>-0.2516</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3364000000000003</v>
+        <v>0.693100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.156999999999998</v>
+        <v>8.2072</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.8208</v>
+        <v>-7.514200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>5.920600000000001</v>
+        <v>5.927899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.7019</v>
+        <v>-3.6643</v>
       </c>
       <c r="I13" t="n">
-        <v>9.622199999999999</v>
+        <v>9.591899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>17.1844</v>
+        <v>16.94140000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.337799999999999</v>
+        <v>4.2415</v>
       </c>
       <c r="L13" t="n">
-        <v>12.8467</v>
+        <v>12.6999</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.2638</v>
+        <v>-11.0138</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.039299999999999</v>
+        <v>-7.905599999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2243</v>
+        <v>-3.1081</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7864000000000001</v>
+        <v>-0.4411000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.223000000000001</v>
+        <v>2.5982</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0095</v>
+        <v>-3.0392</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.6636</v>
+        <v>-3.6554</v>
       </c>
       <c r="W13" t="n">
-        <v>4.6281</v>
+        <v>4.602099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.291600000000001</v>
+        <v>-8.257399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5518</v>
+        <v>3.5232</v>
       </c>
       <c r="E14" t="n">
-        <v>5.798</v>
+        <v>4.5771</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2462</v>
+        <v>-1.0539</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1099</v>
+        <v>1.1088</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3608</v>
+        <v>0.3564</v>
       </c>
       <c r="I14" t="n">
-        <v>0.749</v>
+        <v>0.7524</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9428</v>
+        <v>2.9065</v>
       </c>
       <c r="K14" t="n">
-        <v>0.488</v>
+        <v>0.4719</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4548</v>
+        <v>2.4346</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8329</v>
+        <v>-1.7977</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7057</v>
+        <v>-1.6822</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6423</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4166</v>
+        <v>1.2444</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7743</v>
+        <v>-0.622</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7188</v>
+        <v>3.3449</v>
       </c>
       <c r="E15" t="n">
-        <v>2.325</v>
+        <v>3.1081</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3938</v>
+        <v>0.2368</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1571</v>
+        <v>1.1436</v>
       </c>
       <c r="H15" t="n">
-        <v>1.397</v>
+        <v>1.385</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2399</v>
+        <v>-0.2414</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4991</v>
+        <v>3.4629</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0118</v>
+        <v>1.9887</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.342</v>
+        <v>-2.3193</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.529</v>
+        <v>0.1103</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.747</v>
+        <v>0.0809</v>
       </c>
       <c r="U15" t="n">
-        <v>0.218</v>
+        <v>0.0294</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2707</v>
+        <v>3.145</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3405</v>
+        <v>3.4795</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9302</v>
+        <v>-0.3345</v>
       </c>
       <c r="G16" t="n">
-        <v>1.494</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8729</v>
+        <v>-0.2245</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6211</v>
+        <v>0.8924</v>
       </c>
       <c r="J16" t="n">
-        <v>1.768</v>
+        <v>2.2395</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9524</v>
+        <v>0.2068</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8156</v>
+        <v>2.0327</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.274</v>
+        <v>-1.5717</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0795</v>
+        <v>-0.4314</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1945</v>
+        <v>-1.1403</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1642</v>
+        <v>-0.3635</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3871</v>
+        <v>0.2203</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2229</v>
+        <v>-0.5838</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0314</v>
+        <v>2.4976</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3454</v>
+        <v>1.3208</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.314</v>
+        <v>1.1768</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9742</v>
+        <v>1.4986</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3765</v>
+        <v>0.8758</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4024</v>
+        <v>0.6227</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2153</v>
+        <v>1.7519</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9914</v>
+        <v>0.948</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2239</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2411</v>
+        <v>-0.2533</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6149</v>
+        <v>-0.0722</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6263</v>
+        <v>-0.1811</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8985</v>
+        <v>0.3845</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3984</v>
+        <v>0.3899</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5</v>
+        <v>-0.0055</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.996</v>
+        <v>1.4799</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6735</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6775</v>
+        <v>-0.4202</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6564</v>
+        <v>-0.2554</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2339</v>
+        <v>1.8299</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8903</v>
+        <v>-2.0853</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2548</v>
+        <v>3.0652</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2078</v>
+        <v>2.2613</v>
       </c>
       <c r="L18" t="n">
-        <v>2.047</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5984</v>
+        <v>-3.3205</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1567</v>
+        <v>-2.8891</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5016</v>
+        <v>-0.1266</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6079</v>
+        <v>-0.523</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8937</v>
+        <v>0.3964</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1162</v>
+        <v>0.872</v>
       </c>
       <c r="E19" t="n">
-        <v>1.352</v>
+        <v>0.1884</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2358</v>
+        <v>0.6835</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2527</v>
+        <v>0.3911</v>
       </c>
       <c r="H19" t="n">
-        <v>1.837</v>
+        <v>-0.1006</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0897</v>
+        <v>0.4917</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0943</v>
+        <v>0.1607</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2787</v>
+        <v>0.0862</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8156</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.347</v>
+        <v>0.2305</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4417</v>
+        <v>-0.1868</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.9053</v>
+        <v>0.4173</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4969</v>
+        <v>0.2532</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.113</v>
+        <v>0.2554</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6161</v>
+        <v>-0.0022</v>
       </c>
       <c r="V19" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6914</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0475</v>
+        <v>0.6815</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7389</v>
+        <v>-0.0297</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3853</v>
+        <v>0.9919</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1025</v>
+        <v>1.3785</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4878</v>
+        <v>-0.3866</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1612</v>
+        <v>2.2057</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>1.9822</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.2234</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2241</v>
+        <v>-1.2138</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.6037</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4132</v>
+        <v>-0.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0181</v>
+        <v>0.7521</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0611</v>
+        <v>-0.2516</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4731</v>
+        <v>-2.1416</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2352</v>
+        <v>0.5154</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7083</v>
+        <v>-2.6569</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2009</v>
+        <v>-2.2006</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0434</v>
+        <v>0.0349</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2443</v>
+        <v>-2.2355</v>
       </c>
       <c r="J21" t="n">
-        <v>0.219</v>
+        <v>0.2044</v>
       </c>
       <c r="K21" t="n">
-        <v>0.107</v>
+        <v>0.0927</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4198</v>
+        <v>-2.405</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.3563</v>
+        <v>-2.3472</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9131</v>
+        <v>0.238</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0162</v>
+        <v>0.311</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1073</v>
+        <v>-2.7299</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5053</v>
+        <v>0.4802</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6126</v>
+        <v>-3.2101</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2601</v>
+        <v>-1.2684</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1731</v>
+        <v>2.1714</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.4333</v>
+        <v>-3.4398</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5038</v>
+        <v>0.4772</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2685</v>
+        <v>2.258</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7647</v>
+        <v>-1.7808</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7639</v>
+        <v>-1.7457</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4104</v>
+        <v>-0.0338</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3871</v>
+        <v>0.3899</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7976</v>
+        <v>-0.4237</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9386</v>
+        <v>-3.6595</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0318</v>
+        <v>-2.925</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.7345</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1537</v>
+        <v>-1.1473</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4257</v>
+        <v>-1.4246</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2719</v>
+        <v>0.2773</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6425</v>
+        <v>-0.6462</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5113</v>
+        <v>-0.5011</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3312</v>
+        <v>-0.0569</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.121</v>
+        <v>-0.0024</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1937</v>
+        <v>-6.5383</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6749</v>
+        <v>-5.8119</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5188</v>
+        <v>-0.7264</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.8299</v>
+        <v>-6.8579</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.597</v>
+        <v>-2.6182</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.2329</v>
+        <v>-4.2398</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.752</v>
+        <v>-4.814</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6358</v>
+        <v>-1.6697</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1162</v>
+        <v>-3.1443</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0779</v>
+        <v>-2.0439</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1167</v>
+        <v>-1.0954</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6418</v>
+        <v>0.0512</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0253</v>
+        <v>-0.0795</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3835</v>
+        <v>0.1306</v>
       </c>
       <c r="V24" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W24" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3363999999999985</v>
+        <v>0.4450000000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>7.8207</v>
+        <v>7.514100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.157100000000002</v>
+        <v>-7.0691</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.9204</v>
+        <v>-5.927800000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7016</v>
+        <v>3.664000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.622400000000001</v>
+        <v>-9.591899999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>11.2638</v>
+        <v>11.0138</v>
       </c>
       <c r="K25" t="n">
-        <v>8.039299999999999</v>
+        <v>7.905399999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>3.2245</v>
+        <v>3.1082</v>
       </c>
       <c r="M25" t="n">
-        <v>-17.1842</v>
+        <v>-16.9415</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.337800000000001</v>
+        <v>-4.2415</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.8467</v>
+        <v>-12.6997</v>
       </c>
       <c r="P25" t="n">
-        <v>1.134</v>
+        <v>1.138</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.744</v>
+        <v>-14.796</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7864000000000003</v>
+        <v>1.5794</v>
       </c>
       <c r="T25" t="n">
-        <v>3.009299999999999</v>
+        <v>3.039</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2231</v>
+        <v>-1.4599</v>
       </c>
       <c r="V25" t="n">
-        <v>3.6635</v>
+        <v>3.6553</v>
       </c>
       <c r="W25" t="n">
-        <v>8.291600000000001</v>
+        <v>8.257300000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.627999999999999</v>
+        <v>-4.6021</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104669_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104669_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.257399999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104669_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.6021</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
